--- a/ConfigWorkspace/Data/enemy.xlsx
+++ b/ConfigWorkspace/Data/enemy.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,17 +464,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>stun_seconds</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
           <t>hp</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>flash_hz</t>
         </is>
       </c>
     </row>
@@ -526,17 +516,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>float!#range=[0,5]</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
           <t>int!#range=[1,999]</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>float!#range=[0,10]</t>
         </is>
       </c>
     </row>
@@ -591,16 +571,6 @@
           <t>c</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -650,17 +620,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>受击禁足时长</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
           <t>耐久</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>受击闪烁频率</t>
         </is>
       </c>
     </row>
@@ -692,13 +652,7 @@
         <v>60</v>
       </c>
       <c r="J5" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="K5" t="n">
         <v>3</v>
-      </c>
-      <c r="L5" t="n">
-        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/ConfigWorkspace/Data/enemy.xlsx
+++ b/ConfigWorkspace/Data/enemy.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,35 +434,10 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>radius</t>
+          <t>max_speed</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
-        <is>
-          <t>max_speed</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>acceleration</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>knockback_decay</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>stop_distance</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>chase_range</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>hp</t>
         </is>
@@ -486,35 +461,10 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>float!#range=[0.05,5]</t>
+          <t>float!#range=[0,50]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
-        <is>
-          <t>float!#range=[0,50]</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>float!#range=[0,300]</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>float!#range=[0,100]</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>float!#range=[0,10]</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>float!#range=[0,200]</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
         <is>
           <t>int!#range=[1,999]</t>
         </is>
@@ -546,31 +496,6 @@
           <t>c</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -590,35 +515,10 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>视觉与碰撞半径</t>
+          <t>追击满速</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
-        <is>
-          <t>追击满速</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>加速度</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>击退滑行衰减率</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>停止逼近距离</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>放弃追击距离</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
         <is>
           <t>耐久</t>
         </is>
@@ -634,24 +534,9 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.45</v>
+        <v>3.6</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F5" t="n">
-        <v>14</v>
-      </c>
-      <c r="G5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I5" t="n">
-        <v>60</v>
-      </c>
-      <c r="J5" t="n">
         <v>3</v>
       </c>
     </row>

--- a/ConfigWorkspace/Data/enemy.xlsx
+++ b/ConfigWorkspace/Data/enemy.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -422,24 +422,29 @@
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>max_speed</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>hp</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>contact_damage</t>
         </is>
       </c>
     </row>
@@ -449,24 +454,29 @@
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>string!</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>float!#range=[0,50]</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>int!#range=[1,999]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>int!#range=[0,999]</t>
         </is>
       </c>
     </row>
@@ -476,22 +486,27 @@
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>c</t>
         </is>
@@ -503,41 +518,68 @@
           <t>##comment</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>编号</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>显示名</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>追击满速</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>耐久</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>贴身一次造成的伤害</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="n">
+      <c r="E5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>白模敌人</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>普通怪</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H5" t="n">
         <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>精英怪</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/ConfigWorkspace/Data/enemy.xlsx
+++ b/ConfigWorkspace/Data/enemy.xlsx
@@ -1,34 +1,121 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6166C9BF-8C11-4E3A-9A92-59DF4C64ED38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="3945" yWindow="3810" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+  <si>
+    <t>##var</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>max_speed</t>
+  </si>
+  <si>
+    <t>hp</t>
+  </si>
+  <si>
+    <t>contact_damage</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string!</t>
+  </si>
+  <si>
+    <t>float!#range=[0,50]</t>
+  </si>
+  <si>
+    <t>int!#range=[1,999]</t>
+  </si>
+  <si>
+    <t>int!#range=[0,999]</t>
+  </si>
+  <si>
+    <t>##group</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>##comment</t>
+  </si>
+  <si>
+    <t>编号</t>
+  </si>
+  <si>
+    <t>显示名</t>
+  </si>
+  <si>
+    <t>追击满速</t>
+  </si>
+  <si>
+    <t>耐久</t>
+  </si>
+  <si>
+    <t>贴身一次造成的伤害</t>
+  </si>
+  <si>
+    <t>普通怪</t>
+  </si>
+  <si>
+    <t>精英怪</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +134,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,181 +436,133 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="2" max="2" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="20.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>max_speed</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>hp</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>contact_damage</t>
-        </is>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>##type</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>string!</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>float!#range=[0,50]</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>int!#range=[1,999]</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>int!#range=[0,999]</t>
-        </is>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>##group</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>##comment</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>编号</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>显示名</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>追击满速</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>耐久</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>贴身一次造成的伤害</t>
-        </is>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="5">
-      <c r="E5" t="n">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B5">
         <v>1</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>普通怪</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5">
         <v>3.5</v>
       </c>
-      <c r="H5" t="n">
+      <c r="E5">
         <v>3</v>
       </c>
-      <c r="I5" t="n">
+      <c r="F5">
         <v>1</v>
       </c>
     </row>
-    <row r="6">
-      <c r="E6" t="n">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B6">
         <v>2</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>精英怪</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6">
         <v>4.2</v>
       </c>
-      <c r="H6" t="n">
+      <c r="E6">
         <v>6</v>
       </c>
-      <c r="I6" t="n">
+      <c r="F6">
         <v>2</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ConfigWorkspace/Data/enemy.xlsx
+++ b/ConfigWorkspace/Data/enemy.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnityHub\Unity Project\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6166C9BF-8C11-4E3A-9A92-59DF4C64ED38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E72E8F7-2015-45F6-96DB-E58A273B4F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3945" yWindow="3810" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4248" yWindow="2796" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -81,9 +81,6 @@
     <t>追击满速</t>
   </si>
   <si>
-    <t>耐久</t>
-  </si>
-  <si>
     <t>贴身一次造成的伤害</t>
   </si>
   <si>
@@ -91,6 +88,10 @@
   </si>
   <si>
     <t>精英怪</t>
+  </si>
+  <si>
+    <t>生命值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -438,15 +439,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="20.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -466,7 +467,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -486,7 +487,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -506,7 +507,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -520,18 +521,18 @@
         <v>17</v>
       </c>
       <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
         <v>18</v>
       </c>
-      <c r="F4" t="s">
-        <v>19</v>
-      </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D5">
         <v>3.5</v>
@@ -543,12 +544,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D6">
         <v>4.2</v>

--- a/ConfigWorkspace/Data/enemy.xlsx
+++ b/ConfigWorkspace/Data/enemy.xlsx
@@ -1,24 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnityHub\Unity Project\deepseaoil\ConfigWorkspace\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E72E8F7-2015-45F6-96DB-E58A273B4F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4248" yWindow="2796" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="14940" windowHeight="9900"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -81,6 +83,9 @@
     <t>追击满速</t>
   </si>
   <si>
+    <t>生命值</t>
+  </si>
+  <si>
     <t>贴身一次造成的伤害</t>
   </si>
   <si>
@@ -88,41 +93,373 @@
   </si>
   <si>
     <t>精英怪</t>
-  </si>
-  <si>
-    <t>生命值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -130,24 +467,310 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -432,22 +1055,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="5"/>
   <cols>
-    <col min="2" max="2" width="5.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.21818181818182" customWidth="1"/>
+    <col min="3" max="3" width="8.44545454545455" customWidth="1"/>
+    <col min="4" max="4" width="21.6636363636364" customWidth="1"/>
+    <col min="5" max="6" width="20.4454545454545" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -467,7 +1090,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -487,7 +1110,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -507,7 +1130,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -521,21 +1144,21 @@
         <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:6">
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -544,12 +1167,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6">
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6">
         <v>4.2</v>
@@ -562,8 +1185,8 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ConfigWorkspace/Data/enemy.xlsx
+++ b/ConfigWorkspace/Data/enemy.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14940" windowHeight="9900"/>
+    <workbookView windowWidth="15160" windowHeight="10460"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -105,14 +105,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -568,148 +561,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1158,7 +1151,7 @@
         <v>20</v>
       </c>
       <c r="D5">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="E5">
         <v>3</v>

--- a/ConfigWorkspace/Data/enemy.xlsx
+++ b/ConfigWorkspace/Data/enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E08CF958-B799-4E27-B0B9-DFC2BEFCCBEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1FC476E-1149-4C8B-B196-BBB139604A09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2565" yWindow="7965" windowWidth="19785" windowHeight="13635" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1380" yWindow="4110" windowWidth="19785" windowHeight="15525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
   <si>
     <t>##var</t>
   </si>
@@ -91,39 +91,6 @@
   </si>
   <si>
     <t>精英怪</t>
-  </si>
-  <si>
-    <t>drop_seeds</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>l</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ist,dso.SeedType</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>c</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>掉落种子列表(分号分割，留空不掉落)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1;2;3;4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -491,7 +458,7 @@
     <col min="3" max="3" width="8.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="21.625" style="1" customWidth="1"/>
     <col min="5" max="6" width="20.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="36.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.15">
@@ -513,9 +480,6 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>22</v>
-      </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
@@ -536,9 +500,7 @@
       <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>23</v>
-      </c>
+      <c r="G2" s="2"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
@@ -559,9 +521,7 @@
       <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>24</v>
-      </c>
+      <c r="G3" s="2"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
@@ -582,9 +542,7 @@
       <c r="F4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.15">
       <c r="B5" s="1">
@@ -619,9 +577,6 @@
       </c>
       <c r="F6" s="1">
         <v>2</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/ConfigWorkspace/Data/enemy.xlsx
+++ b/ConfigWorkspace/Data/enemy.xlsx
@@ -1,24 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1FC476E-1149-4C8B-B196-BBB139604A09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="4110" windowWidth="19785" windowHeight="15525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="15160" windowHeight="10460"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -96,8 +98,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,29 +114,345 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -136,30 +460,310 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -444,144 +1048,138 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="5.25" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.625" style="1" customWidth="1"/>
-    <col min="5" max="6" width="20.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="5.21818181818182" customWidth="1"/>
+    <col min="3" max="3" width="8.44545454545455" customWidth="1"/>
+    <col min="4" max="4" width="21.6636363636364" customWidth="1"/>
+    <col min="5" max="6" width="20.4454545454545" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="2"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="2"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="B5" s="1">
+    <row r="5" spans="2:6">
+      <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="1">
-        <v>3.1</v>
-      </c>
-      <c r="E5" s="1">
+      <c r="D5">
+        <v>3.5</v>
+      </c>
+      <c r="E5">
         <v>3</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5">
         <v>1</v>
       </c>
-      <c r="G5" s="2"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="B6" s="1">
+    <row r="6" spans="2:6">
+      <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6">
         <v>4.2</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6">
         <v>6</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ConfigWorkspace/Data/enemy.xlsx
+++ b/ConfigWorkspace/Data/enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CF9DDFA-DDDC-4C55-93BA-6AC8C4ED7301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD50C688-1E43-44D2-A20A-A6C0CD97B66A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6460" yWindow="1460" windowWidth="15080" windowHeight="11670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3105" yWindow="3300" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -489,17 +489,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="5.1796875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.453125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6328125" style="1" customWidth="1"/>
-    <col min="5" max="6" width="20.453125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="35.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21.625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="20.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -522,7 +522,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -545,7 +545,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -568,7 +568,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -591,7 +591,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
       <c r="B5" s="1">
         <v>1</v>
       </c>
@@ -599,7 +599,7 @@
         <v>20</v>
       </c>
       <c r="D5" s="1">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="E5" s="1">
         <v>3</v>
@@ -611,7 +611,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
       <c r="B6" s="1">
         <v>2</v>
       </c>
@@ -619,7 +619,7 @@
         <v>21</v>
       </c>
       <c r="D6" s="1">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="E6" s="1">
         <v>8</v>

--- a/ConfigWorkspace/Data/enemy.xlsx
+++ b/ConfigWorkspace/Data/enemy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD50C688-1E43-44D2-A20A-A6C0CD97B66A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF269F8C-9A5D-4B8B-8256-6AC204BF06AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3105" yWindow="3300" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -599,7 +599,7 @@
         <v>20</v>
       </c>
       <c r="D5" s="1">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="E5" s="1">
         <v>3</v>
@@ -619,7 +619,7 @@
         <v>21</v>
       </c>
       <c r="D6" s="1">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="E6" s="1">
         <v>8</v>

--- a/ConfigWorkspace/Data/enemy.xlsx
+++ b/ConfigWorkspace/Data/enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CF9DDFA-DDDC-4C55-93BA-6AC8C4ED7301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF269F8C-9A5D-4B8B-8256-6AC204BF06AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6460" yWindow="1460" windowWidth="15080" windowHeight="11670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3105" yWindow="3300" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -489,17 +489,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="5.1796875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.453125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6328125" style="1" customWidth="1"/>
-    <col min="5" max="6" width="20.453125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="35.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21.625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="20.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -522,7 +522,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -545,7 +545,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -568,7 +568,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -591,7 +591,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
       <c r="B5" s="1">
         <v>1</v>
       </c>
@@ -599,7 +599,7 @@
         <v>20</v>
       </c>
       <c r="D5" s="1">
-        <v>2.8</v>
+        <v>7.2</v>
       </c>
       <c r="E5" s="1">
         <v>3</v>
@@ -611,7 +611,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
       <c r="B6" s="1">
         <v>2</v>
       </c>
@@ -619,7 +619,7 @@
         <v>21</v>
       </c>
       <c r="D6" s="1">
-        <v>3.4</v>
+        <v>8.6</v>
       </c>
       <c r="E6" s="1">
         <v>8</v>

--- a/ConfigWorkspace/Data/enemy.xlsx
+++ b/ConfigWorkspace/Data/enemy.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnityHub\Unity Project\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF269F8C-9A5D-4B8B-8256-6AC204BF06AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09213381-EB0C-4A57-A6F9-B8AFC7195BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3105" yWindow="3300" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3168" yWindow="1812" windowWidth="17280" windowHeight="11448" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -489,17 +489,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="5.125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.625" style="1" customWidth="1"/>
-    <col min="5" max="6" width="20.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="35.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="20.44140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -522,7 +522,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -545,7 +545,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -568,7 +568,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -591,7 +591,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>1</v>
       </c>
@@ -602,7 +602,7 @@
         <v>7.2</v>
       </c>
       <c r="E5" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
@@ -611,7 +611,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>2</v>
       </c>
@@ -622,7 +622,7 @@
         <v>8.6</v>
       </c>
       <c r="E6" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F6" s="1">
         <v>2</v>

--- a/ConfigWorkspace/Data/enemy.xlsx
+++ b/ConfigWorkspace/Data/enemy.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnityHub\Unity Project\deepseaoil\ConfigWorkspace\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09213381-EB0C-4A57-A6F9-B8AFC7195BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8E10B46-187D-4FF2-91F1-E6A3C9A956E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3168" yWindow="1812" windowWidth="17280" windowHeight="11448" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14385" yWindow="4695" windowWidth="18345" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -489,17 +489,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="5.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" style="1" customWidth="1"/>
-    <col min="5" max="6" width="20.44140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="35.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21.625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="20.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -522,7 +522,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -545,7 +545,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -568,7 +568,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -591,7 +591,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
       <c r="B5" s="1">
         <v>1</v>
       </c>
@@ -602,7 +602,7 @@
         <v>7.2</v>
       </c>
       <c r="E5" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
@@ -611,7 +611,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
       <c r="B6" s="1">
         <v>2</v>
       </c>
@@ -622,7 +622,7 @@
         <v>8.6</v>
       </c>
       <c r="E6" s="1">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F6" s="1">
         <v>2</v>
